--- a/docs/My_Professional_Reviews/UAS_Skor.xlsx
+++ b/docs/My_Professional_Reviews/UAS_Skor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sekolah\Tahun 2\Semester 3\all-about-me\My_Professional_Reviews\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FB7BD7-9473-4AA4-8AE5-2BB90F81E8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEEDB586-2B27-4AF6-945E-75B65D59522F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
   </bookViews>
@@ -175,16 +175,16 @@
     <t>Otomatis</t>
   </si>
   <si>
-    <t>Tyara Penelope Lumban Gaol</t>
-  </si>
-  <si>
     <t>Daniel Wicaksana Godjali (Self Assessment)</t>
   </si>
   <si>
-    <t>Muhamad Radhitya Alamsyah</t>
-  </si>
-  <si>
-    <t>Andreas Saputra Tambun</t>
+    <t>Aisyah Az Zahra</t>
+  </si>
+  <si>
+    <t>Ayudia Nisrina Tsabitah</t>
+  </si>
+  <si>
+    <t>Rian Albar Insani</t>
   </si>
 </sst>
 </file>
@@ -849,7 +849,7 @@
         <v>18224114</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" s="2">
         <v>4</v>
@@ -934,26 +934,26 @@
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>18224122</v>
+        <v>11422020</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C4" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="H4" s="2">
         <v>5</v>
@@ -962,20 +962,20 @@
         <v>5</v>
       </c>
       <c r="J4" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K4" s="2">
         <v>5</v>
       </c>
       <c r="L4" s="4">
         <f t="shared" si="1"/>
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O4" s="2">
         <v>5</v>
@@ -985,82 +985,130 @@
       </c>
       <c r="Q4" s="4">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V4" s="4">
         <f t="shared" si="3"/>
-        <v>3.25</v>
-      </c>
-      <c r="AA4" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AF4" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK4" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AP4" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="W4" s="2">
+        <v>5</v>
+      </c>
+      <c r="X4" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>5</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AA4" s="4">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AD4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AE4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AF4" s="4">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AG4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AH4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AI4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AJ4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AK4" s="4">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="AL4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AM4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AN4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AO4" s="2">
+        <v>5</v>
+      </c>
+      <c r="AP4" s="4">
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>18224126</v>
+        <v>14324016</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C5" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="H5" s="2">
         <v>5</v>
       </c>
       <c r="I5" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L5" s="4">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M5" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N5" s="2">
         <v>5</v>
@@ -1073,63 +1121,111 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="2"/>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="R5" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S5" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" s="2">
         <v>5</v>
       </c>
       <c r="U5" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V5" s="4">
         <f t="shared" si="3"/>
-        <v>3.5</v>
-      </c>
-      <c r="AA5" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AF5" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK5" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AP5" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="W5" s="2">
+        <v>5</v>
+      </c>
+      <c r="X5" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>5</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AA5" s="4">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AD5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AE5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AF5" s="4">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AG5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AH5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AI5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AJ5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AK5" s="4">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="AL5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AM5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AN5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AO5" s="2">
+        <v>5</v>
+      </c>
+      <c r="AP5" s="4">
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>18224110</v>
+        <v>18224121</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G6" s="4">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="H6" s="2">
         <v>5</v>
@@ -1138,62 +1234,110 @@
         <v>5</v>
       </c>
       <c r="J6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" s="4">
         <f t="shared" si="1"/>
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="M6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q6" s="4">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R6" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" s="2">
         <v>5</v>
       </c>
       <c r="U6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V6" s="4">
         <f t="shared" si="3"/>
-        <v>3.5</v>
-      </c>
-      <c r="AA6" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AF6" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AK6" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AP6" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="W6" s="2">
+        <v>5</v>
+      </c>
+      <c r="X6" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>5</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AA6" s="4">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AE6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AF6" s="4">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="AG6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AH6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AI6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AJ6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AK6" s="4">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="AL6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AM6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AN6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AO6" s="2">
+        <v>5</v>
+      </c>
+      <c r="AP6" s="4">
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.3">
@@ -3782,13 +3926,13 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Skor 1–5" prompt="Masukkan nilai antara 1 dan 5 (boleh desimal)." sqref="AL3:AO82 AG3:AJ82 AB3:AE82 W3:Z82 R3:U82 M3:P82 H3:K82 C3:F82" xr:uid="{B0F61EF9-DC4B-1D4B-A700-95D0E3F024E2}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Skor 1–5" prompt="Masukkan nilai antara 1 dan 5 (boleh desimal)." sqref="AG3:AJ82 AB3:AE82 W3:Z82 C3:F82 R3:U82 M3:P82 H3:K82 AL3:AO82" xr:uid="{B0F61EF9-DC4B-1D4B-A700-95D0E3F024E2}">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/docs/My_Professional_Reviews/UAS_Skor.xlsx
+++ b/docs/My_Professional_Reviews/UAS_Skor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sekolah\Tahun 2\Semester 3\all-about-me\My_Professional_Reviews\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEEDB586-2B27-4AF6-945E-75B65D59522F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5850A8D9-3E73-41B0-8EF5-DB9EF2C924CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
   </bookViews>
@@ -16,6 +16,10 @@
     <sheet name="Scores" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_Toc231198312" localSheetId="0">Scores!$AB$2</definedName>
+    <definedName name="_Toc713889184" localSheetId="0">Scores!$AB$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -915,21 +919,69 @@
         <f t="shared" ref="V3:V66" si="3">IF(COUNT(R3:U3)=0,"",AVERAGE(R3:U3))</f>
         <v>3</v>
       </c>
-      <c r="AA3" s="4" t="str">
+      <c r="W3" s="2">
+        <v>4</v>
+      </c>
+      <c r="X3" s="2">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>4</v>
+      </c>
+      <c r="AA3" s="4">
         <f t="shared" ref="AA3:AA66" si="4">IF(COUNT(W3:Z3)=0,"",AVERAGE(W3:Z3))</f>
-        <v/>
-      </c>
-      <c r="AF3" s="4" t="str">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>4</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>4</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>4</v>
+      </c>
+      <c r="AE3" s="2">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="4">
         <f t="shared" ref="AF3:AF66" si="5">IF(COUNT(AB3:AE3)=0,"",AVERAGE(AB3:AE3))</f>
-        <v/>
-      </c>
-      <c r="AK3" s="4" t="str">
+        <v>4</v>
+      </c>
+      <c r="AG3" s="2">
+        <v>4</v>
+      </c>
+      <c r="AH3" s="2">
+        <v>5</v>
+      </c>
+      <c r="AI3" s="2">
+        <v>4</v>
+      </c>
+      <c r="AJ3" s="2">
+        <v>4</v>
+      </c>
+      <c r="AK3" s="4">
         <f t="shared" ref="AK3:AK66" si="6">IF(COUNT(AG3:AJ3)=0,"",AVERAGE(AG3:AJ3))</f>
-        <v/>
-      </c>
-      <c r="AP3" s="4" t="str">
+        <v>4.25</v>
+      </c>
+      <c r="AL3" s="2">
+        <v>5</v>
+      </c>
+      <c r="AM3" s="2">
+        <v>4</v>
+      </c>
+      <c r="AN3" s="2">
+        <v>4</v>
+      </c>
+      <c r="AO3" s="2">
+        <v>4</v>
+      </c>
+      <c r="AP3" s="4">
         <f t="shared" ref="AP3:AP66" si="7">IF(COUNT(AL3:AO3)=0,"",AVERAGE(AL3:AO3))</f>
-        <v/>
+        <v>4.25</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.3">
